--- a/Yakuniy nazorat/4-kurs/AT/Natijalar/AT-4.4-22.xlsx
+++ b/Yakuniy nazorat/4-kurs/AT/Natijalar/AT-4.4-22.xlsx
@@ -1,23 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dars SIA\Yakuniy nazorat\4.4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2025-2026\Git\Yakuniy nazorat\4-kurs\AT\Natijalar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F8BD4B1-D1AE-4FB5-B626-50D81DF0E3C1}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68B9C8F6-DAAC-415D-9E12-8AFE075A4772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JN+ON+YN" sheetId="1" r:id="rId1"/>
     <sheet name="JN+YN" sheetId="5" r:id="rId2"/>
     <sheet name="JN" sheetId="6" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="179021"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1081,9 +1095,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>54</xdr:col>
-      <xdr:colOff>145415</xdr:colOff>
+      <xdr:colOff>142875</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>89535</xdr:rowOff>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1098,8 +1112,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12348696" y="7552914"/>
-          <a:ext cx="2308337" cy="492797"/>
+          <a:off x="12461875" y="7602220"/>
+          <a:ext cx="2330450" cy="484505"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -1531,20 +1545,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BC1000"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.109375" customWidth="1"/>
-    <col min="2" max="2" width="23.33203125" customWidth="1"/>
-    <col min="3" max="24" width="3.5546875" customWidth="1"/>
-    <col min="25" max="25" width="3.44140625" customWidth="1"/>
-    <col min="26" max="26" width="3.88671875" customWidth="1"/>
-    <col min="27" max="52" width="3.5546875" customWidth="1"/>
-    <col min="53" max="53" width="8.33203125" customWidth="1"/>
-    <col min="54" max="54" width="6.33203125" customWidth="1"/>
-    <col min="55" max="55" width="4.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.140625" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" customWidth="1"/>
+    <col min="3" max="24" width="3.5703125" customWidth="1"/>
+    <col min="25" max="25" width="3.42578125" customWidth="1"/>
+    <col min="26" max="26" width="3.85546875" customWidth="1"/>
+    <col min="27" max="52" width="3.5703125" customWidth="1"/>
+    <col min="53" max="53" width="8.28515625" customWidth="1"/>
+    <col min="54" max="54" width="6.28515625" customWidth="1"/>
+    <col min="55" max="55" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:54" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
@@ -1600,7 +1614,7 @@
       <c r="AY1" s="24"/>
       <c r="AZ1" s="25"/>
     </row>
-    <row r="2" spans="1:54" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:54" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="29" t="s">
         <v>1</v>
       </c>
@@ -1702,7 +1716,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:54" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:54" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="27"/>
       <c r="B3" s="27"/>
       <c r="C3" s="2" t="s">
@@ -1862,7 +1876,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:54" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:54" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>1</v>
       </c>
@@ -1960,7 +1974,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:54" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:54" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>2</v>
       </c>
@@ -2060,7 +2074,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="1:54" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:54" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>3</v>
       </c>
@@ -2160,7 +2174,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="7" spans="1:54" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:54" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>4</v>
       </c>
@@ -2260,7 +2274,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="8" spans="1:54" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:54" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>5</v>
       </c>
@@ -2364,7 +2378,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="9" spans="1:54" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:54" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>6</v>
       </c>
@@ -2464,7 +2478,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="10" spans="1:54" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:54" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>7</v>
       </c>
@@ -2558,7 +2572,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="11" spans="1:54" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:54" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>8</v>
       </c>
@@ -2652,7 +2666,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:54" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:54" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>9</v>
       </c>
@@ -2750,7 +2764,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="1:54" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:54" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>10</v>
       </c>
@@ -2814,7 +2828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:54" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:54" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>11</v>
       </c>
@@ -2878,7 +2892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:54" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:54" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>12</v>
       </c>
@@ -2942,8 +2956,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:54" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="17" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:54" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="AI17" s="10"/>
       <c r="AJ17" s="10"/>
       <c r="AK17" s="10"/>
@@ -2959,7 +2973,7 @@
       <c r="AU17" s="10"/>
       <c r="AV17" s="10"/>
     </row>
-    <row r="18" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
         <v>64</v>
       </c>
@@ -2987,7 +3001,7 @@
       <c r="W18" s="24"/>
       <c r="X18" s="25"/>
     </row>
-    <row r="19" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="29" t="s">
         <v>1</v>
       </c>
@@ -3035,7 +3049,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:55" ht="76.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:55" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="27"/>
       <c r="B20" s="27"/>
       <c r="C20" s="13" t="s">
@@ -3149,7 +3163,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="21" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16">
         <v>1</v>
       </c>
@@ -3229,22 +3243,24 @@
       </c>
       <c r="AS21" s="21"/>
       <c r="AT21" s="22"/>
-      <c r="AU21" s="20"/>
+      <c r="AU21" s="20">
+        <v>27</v>
+      </c>
       <c r="AV21" s="21"/>
       <c r="AW21" s="22"/>
       <c r="AX21" s="20">
         <f>ROUND(SUM(AR21:AW21),0)</f>
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="AY21" s="21"/>
       <c r="AZ21" s="21"/>
       <c r="BA21" s="17">
         <f>IF(AND(AX21&gt;=0,AX21&lt;55),2,IF(AND(AX21&gt;=55,AX21&lt;71),3,IF(AND(AX21&gt;=71,AX21&lt;86),4,IF(AND(AX21&gt;=86,AX20&lt;=100),5,5))))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BC21" s="18"/>
     </row>
-    <row r="22" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>2</v>
       </c>
@@ -3324,21 +3340,23 @@
       </c>
       <c r="AS22" s="21"/>
       <c r="AT22" s="22"/>
-      <c r="AU22" s="20"/>
+      <c r="AU22" s="20">
+        <v>30</v>
+      </c>
       <c r="AV22" s="21"/>
       <c r="AW22" s="22"/>
       <c r="AX22" s="20">
         <f t="shared" ref="AX22:AX32" si="10">ROUND(SUM(AR22:AW22),0)</f>
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="AY22" s="21"/>
       <c r="AZ22" s="21"/>
       <c r="BA22" s="17">
         <f t="shared" ref="BA22:BA32" si="11">IF(AND(AX22&gt;=0,AX22&lt;55),2,IF(AND(AX22&gt;=55,AX22&lt;71),3,IF(AND(AX22&gt;=71,AX22&lt;86),4,IF(AND(AX22&gt;=86,AX21&lt;=100),5,5))))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>3</v>
       </c>
@@ -3418,21 +3436,23 @@
       </c>
       <c r="AS23" s="21"/>
       <c r="AT23" s="22"/>
-      <c r="AU23" s="20"/>
+      <c r="AU23" s="20">
+        <v>20</v>
+      </c>
       <c r="AV23" s="21"/>
       <c r="AW23" s="22"/>
       <c r="AX23" s="20">
         <f t="shared" si="10"/>
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="AY23" s="21"/>
       <c r="AZ23" s="21"/>
       <c r="BA23" s="17">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>4</v>
       </c>
@@ -3528,7 +3548,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>5</v>
       </c>
@@ -3624,7 +3644,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>6</v>
       </c>
@@ -3720,7 +3740,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>7</v>
       </c>
@@ -3800,21 +3820,23 @@
       </c>
       <c r="AS27" s="21"/>
       <c r="AT27" s="22"/>
-      <c r="AU27" s="20"/>
+      <c r="AU27" s="20">
+        <v>30</v>
+      </c>
       <c r="AV27" s="21"/>
       <c r="AW27" s="22"/>
       <c r="AX27" s="20">
         <f t="shared" si="10"/>
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="AY27" s="21"/>
       <c r="AZ27" s="21"/>
       <c r="BA27" s="17">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>8</v>
       </c>
@@ -3894,21 +3916,23 @@
       </c>
       <c r="AS28" s="21"/>
       <c r="AT28" s="22"/>
-      <c r="AU28" s="20"/>
+      <c r="AU28" s="20">
+        <v>28</v>
+      </c>
       <c r="AV28" s="21"/>
       <c r="AW28" s="22"/>
       <c r="AX28" s="20">
         <f t="shared" si="10"/>
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="AY28" s="21"/>
       <c r="AZ28" s="21"/>
       <c r="BA28" s="17">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>9</v>
       </c>
@@ -4004,7 +4028,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>10</v>
       </c>
@@ -4086,7 +4110,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="31" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>11</v>
       </c>
@@ -4168,7 +4192,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="32" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>12</v>
       </c>
@@ -4250,974 +4274,974 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="34" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="36" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="37" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="38" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="40" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="41" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="42" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="43" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="44" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="45" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="47" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="48" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="49" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="50" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="51" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="52" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="53" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="54" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="55" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="56" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="57" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="58" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="59" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="60" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="61" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="62" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="63" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="64" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="65" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="66" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="67" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="68" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="69" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="70" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="71" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="72" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="73" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="74" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="75" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="76" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="77" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="78" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="79" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="80" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="81" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="82" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="83" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="84" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="85" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="86" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="87" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="88" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="89" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="90" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="91" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="92" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="93" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="94" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="95" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="96" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="97" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="98" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="99" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="100" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="101" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="102" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="103" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="104" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="105" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="106" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="107" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="108" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="109" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="110" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="111" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="112" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="113" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="114" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="115" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="116" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="117" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="118" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="119" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="120" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="121" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="122" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="123" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="124" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="125" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="126" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="127" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="128" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="129" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="130" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="131" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="132" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="133" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="134" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="135" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="136" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="137" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="138" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="139" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="140" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="141" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="142" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="143" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="144" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="145" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="146" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="147" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="148" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="149" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="150" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="151" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="152" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="153" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="154" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="155" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="156" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="157" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="158" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="159" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="160" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="161" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="162" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="163" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="164" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="165" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="166" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="167" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="168" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="169" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="170" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="171" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="172" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="173" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="174" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="175" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="176" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="177" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="178" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="179" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="180" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="181" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="182" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="183" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="184" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="185" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="186" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="187" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="188" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="189" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="190" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="191" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="192" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="193" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="194" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="195" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="196" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="197" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="198" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="199" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="200" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="201" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="202" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="203" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="204" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="205" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="206" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="207" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="208" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="209" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="210" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="211" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="212" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="213" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="214" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="215" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="216" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="217" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="218" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="219" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="220" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="221" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="222" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="223" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="224" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="225" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="226" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="227" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="228" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="229" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="230" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="231" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="232" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="233" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="234" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="235" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="236" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="237" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="238" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="239" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="240" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="241" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="242" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="243" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="244" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="245" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="246" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="247" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="248" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="249" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="250" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="251" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="252" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="253" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="254" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="255" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="256" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="257" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="258" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="259" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="260" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="261" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="262" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="263" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="264" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="265" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="266" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="267" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="268" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="269" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="270" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="271" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="272" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="273" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="274" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="275" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="276" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="277" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="278" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="279" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="280" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="281" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="282" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="283" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="284" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="285" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="286" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="287" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="288" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="289" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="290" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="291" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="292" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="293" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="294" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="295" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="296" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="297" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="298" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="299" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="300" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="301" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="302" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="303" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="304" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="305" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="306" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="307" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="308" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="309" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="310" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="311" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="312" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="313" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="314" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="315" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="316" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="317" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="318" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="319" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="320" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="321" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="322" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="323" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="324" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="325" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="326" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="327" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="328" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="329" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="330" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="331" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="332" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="333" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="334" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="335" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="336" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="337" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="338" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="339" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="340" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="341" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="342" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="343" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="344" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="345" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="346" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="347" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="348" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="349" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="350" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="351" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="352" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="353" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="354" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="355" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="356" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="357" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="358" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="359" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="360" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="361" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="362" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="363" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="364" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="365" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="366" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="367" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="368" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="369" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="370" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="371" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="372" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="373" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="374" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="375" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="376" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="377" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="378" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="379" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="380" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="381" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="382" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="383" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="384" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="385" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="386" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="387" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="388" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="389" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="390" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="391" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="392" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="393" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="394" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="395" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="396" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="397" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="398" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="399" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="400" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="401" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="402" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="403" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="404" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="405" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="406" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="407" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="408" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="409" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="410" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="411" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="412" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="413" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="414" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="415" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="416" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="417" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="418" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="419" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="420" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="421" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="422" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="423" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="424" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="425" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="426" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="427" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="428" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="429" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="430" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="431" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="432" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="433" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="434" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="435" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="436" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="437" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="438" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="439" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="440" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="441" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="442" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="443" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="444" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="445" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="446" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="447" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="448" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="449" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="450" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="451" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="452" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="453" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="454" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="455" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="456" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="457" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="458" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="459" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="460" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="461" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="462" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="463" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="464" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="465" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="466" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="467" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="468" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="469" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="470" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="471" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="472" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="473" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="474" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="475" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="476" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="477" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="478" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="479" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="480" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="481" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="482" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="483" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="484" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="485" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="486" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="487" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="488" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="489" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="490" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="491" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="492" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="493" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="494" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="495" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="496" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="497" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="498" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="499" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="500" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="501" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="502" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="503" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="504" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="505" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="506" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="507" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="508" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="509" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="510" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="511" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="512" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="513" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="514" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="515" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="516" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="517" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="518" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="519" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="520" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="521" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="522" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="523" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="524" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="525" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="526" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="527" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="528" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="529" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="530" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="531" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="532" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="533" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="534" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="535" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="536" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="537" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="538" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="539" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="540" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="541" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="542" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="543" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="544" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="545" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="546" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="547" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="548" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="549" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="550" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="551" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="552" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="553" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="554" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="555" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="556" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="557" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="558" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="559" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="560" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="561" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="562" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="563" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="564" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="565" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="566" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="567" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="568" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="569" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="570" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="571" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="572" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="573" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="574" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="575" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="576" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="577" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="578" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="579" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="580" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="581" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="582" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="583" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="584" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="585" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="586" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="587" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="588" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="589" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="590" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="591" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="592" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="593" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="594" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="595" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="596" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="597" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="598" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="599" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="600" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="601" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="602" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="603" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="604" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="605" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="606" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="607" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="608" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="609" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="610" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="611" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="612" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="613" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="614" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="615" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="616" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="617" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="618" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="619" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="620" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="621" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="622" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="623" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="624" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="625" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="626" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="627" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="628" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="629" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="630" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="631" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="632" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="633" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="634" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="635" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="636" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="637" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="638" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="639" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="640" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="641" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="642" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="643" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="644" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="645" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="646" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="647" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="648" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="649" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="650" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="651" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="652" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="653" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="654" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="655" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="656" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="657" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="658" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="659" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="660" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="661" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="662" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="663" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="664" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="665" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="666" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="667" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="668" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="669" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="670" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="671" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="672" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="673" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="674" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="675" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="676" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="677" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="678" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="679" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="680" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="681" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="682" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="683" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="684" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="685" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="686" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="687" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="688" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="689" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="690" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="691" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="692" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="693" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="694" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="695" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="696" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="697" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="698" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="699" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="700" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="701" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="702" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="703" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="704" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="705" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="706" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="707" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="708" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="709" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="710" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="711" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="712" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="713" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="714" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="715" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="716" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="717" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="718" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="719" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="720" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="721" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="722" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="723" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="724" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="725" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="726" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="727" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="728" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="729" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="730" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="731" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="732" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="733" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="734" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="735" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="736" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="737" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="738" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="739" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="740" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="741" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="742" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="743" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="744" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="745" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="746" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="747" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="748" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="749" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="750" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="751" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="752" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="753" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="754" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="755" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="756" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="757" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="758" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="759" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="760" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="761" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="762" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="763" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="764" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="765" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="766" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="767" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="768" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="769" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="770" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="771" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="772" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="773" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="774" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="775" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="776" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="777" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="778" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="779" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="780" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="781" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="782" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="783" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="784" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="785" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="786" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="787" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="788" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="789" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="790" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="791" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="792" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="793" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="794" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="795" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="796" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="797" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="798" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="799" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="800" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="801" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="802" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="803" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="804" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="805" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="806" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="807" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="808" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="809" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="810" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="811" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="812" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="813" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="814" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="815" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="816" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="817" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="818" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="819" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="820" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="821" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="822" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="823" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="824" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="825" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="826" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="827" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="828" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="829" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="830" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="831" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="832" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="833" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="834" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="835" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="836" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="837" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="838" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="839" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="840" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="841" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="842" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="843" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="844" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="845" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="846" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="847" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="848" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="849" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="850" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="851" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="852" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="853" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="854" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="855" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="856" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="857" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="858" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="859" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="860" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="861" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="862" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="863" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="864" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="865" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="866" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="867" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="868" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="869" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="870" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="871" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="872" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="873" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="874" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="875" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="876" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="877" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="878" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="879" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="880" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="881" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="882" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="883" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="884" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="885" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="886" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="887" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="888" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="889" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="890" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="891" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="892" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="893" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="894" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="895" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="896" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="897" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="898" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="899" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="900" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="901" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="902" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="903" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="904" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="905" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="906" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="907" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="908" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="909" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="910" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="911" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="912" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="913" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="914" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="915" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="916" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="917" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="918" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="919" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="920" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="921" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="922" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="923" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="924" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="925" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="926" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="927" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="928" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="929" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="930" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="931" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="932" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="933" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="934" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="935" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="936" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="937" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="938" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="939" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="940" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="941" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="942" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="943" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="944" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="945" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="946" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="947" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="948" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="949" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="950" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="951" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="952" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="953" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="954" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="955" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="956" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="957" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="958" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="959" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="960" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="961" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="962" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="963" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="964" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="965" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="966" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="967" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="968" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="969" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="970" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="971" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="972" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="973" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="974" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="975" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="976" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="977" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="978" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="979" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="980" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="981" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="982" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="983" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="984" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="985" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="986" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="987" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="988" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="989" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="990" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="991" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="992" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="993" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="994" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="995" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="996" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="997" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="998" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="999" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="33" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="976" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="977" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="978" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="979" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="980" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="981" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="986" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="987" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="988" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="989" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="990" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="991" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="992" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="993" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="994" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="995" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="996" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="997" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="998" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="999" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="98">
     <mergeCell ref="AO24:AQ24"/>
@@ -5386,16 +5410,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:BC32"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="26" width="3.6640625" bestFit="1" customWidth="1"/>
-    <col min="27" max="52" width="3.5546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="54" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="26" width="3.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="52" width="3.5703125" bestFit="1" customWidth="1"/>
+    <col min="53" max="54" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
@@ -5451,7 +5475,7 @@
       <c r="AY1" s="24"/>
       <c r="AZ1" s="25"/>
     </row>
-    <row r="2" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A2" s="29" t="s">
         <v>1</v>
       </c>
@@ -5511,7 +5535,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:54" ht="83.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:54" ht="83.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="27"/>
       <c r="B3" s="27"/>
       <c r="C3" s="2" t="s">
@@ -5671,7 +5695,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>1</v>
       </c>
@@ -5757,7 +5781,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>2</v>
       </c>
@@ -5845,7 +5869,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>3</v>
       </c>
@@ -5933,7 +5957,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>4</v>
       </c>
@@ -6019,7 +6043,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>5</v>
       </c>
@@ -6107,7 +6131,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>6</v>
       </c>
@@ -6195,7 +6219,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>7</v>
       </c>
@@ -6259,7 +6283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>8</v>
       </c>
@@ -6323,7 +6347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>9</v>
       </c>
@@ -6387,7 +6411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>10</v>
       </c>
@@ -6451,7 +6475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>11</v>
       </c>
@@ -6515,7 +6539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>12</v>
       </c>
@@ -6579,7 +6603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:55" x14ac:dyDescent="0.25">
       <c r="AK17" s="10"/>
       <c r="AL17" s="11"/>
       <c r="AM17" s="11"/>
@@ -6590,7 +6614,7 @@
       <c r="AR17" s="11"/>
       <c r="AS17" s="10"/>
     </row>
-    <row r="18" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
         <v>64</v>
       </c>
@@ -6618,7 +6642,7 @@
       <c r="W18" s="24"/>
       <c r="X18" s="25"/>
     </row>
-    <row r="19" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A19" s="29" t="s">
         <v>1</v>
       </c>
@@ -6666,7 +6690,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:55" ht="65.400000000000006" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:55" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A20" s="27"/>
       <c r="B20" s="27"/>
       <c r="C20" s="13" t="s">
@@ -6776,7 +6800,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="21" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A21" s="16">
         <v>1</v>
       </c>
@@ -6868,7 +6892,7 @@
       </c>
       <c r="BC21" s="18"/>
     </row>
-    <row r="22" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>2</v>
       </c>
@@ -6959,7 +6983,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>3</v>
       </c>
@@ -7050,7 +7074,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>4</v>
       </c>
@@ -7141,7 +7165,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>5</v>
       </c>
@@ -7232,7 +7256,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>6</v>
       </c>
@@ -7323,7 +7347,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>7</v>
       </c>
@@ -7402,7 +7426,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="28" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>8</v>
       </c>
@@ -7481,7 +7505,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="29" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>9</v>
       </c>
@@ -7560,7 +7584,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="30" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>10</v>
       </c>
@@ -7639,7 +7663,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="31" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>11</v>
       </c>
@@ -7718,7 +7742,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="32" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>12</v>
       </c>
@@ -7964,16 +7988,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:BC32"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="26" width="3.6640625" bestFit="1" customWidth="1"/>
-    <col min="27" max="52" width="3.5546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="54" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="26" width="3.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="52" width="3.5703125" bestFit="1" customWidth="1"/>
+    <col min="53" max="54" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
@@ -8029,7 +8053,7 @@
       <c r="AY1" s="24"/>
       <c r="AZ1" s="25"/>
     </row>
-    <row r="2" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A2" s="29" t="s">
         <v>1</v>
       </c>
@@ -8089,7 +8113,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:54" ht="83.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:54" ht="83.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="27"/>
       <c r="B3" s="27"/>
       <c r="C3" s="2" t="s">
@@ -8249,7 +8273,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>1</v>
       </c>
@@ -8335,7 +8359,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>2</v>
       </c>
@@ -8423,7 +8447,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>3</v>
       </c>
@@ -8511,7 +8535,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>4</v>
       </c>
@@ -8597,7 +8621,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>5</v>
       </c>
@@ -8685,7 +8709,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>6</v>
       </c>
@@ -8773,7 +8797,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>7</v>
       </c>
@@ -8837,7 +8861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>8</v>
       </c>
@@ -8901,7 +8925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>9</v>
       </c>
@@ -8965,7 +8989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>10</v>
       </c>
@@ -9029,7 +9053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>11</v>
       </c>
@@ -9093,7 +9117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>12</v>
       </c>
@@ -9157,7 +9181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:55" x14ac:dyDescent="0.25">
       <c r="AK17" s="10"/>
       <c r="AL17" s="11"/>
       <c r="AM17" s="11"/>
@@ -9168,7 +9192,7 @@
       <c r="AR17" s="11"/>
       <c r="AS17" s="10"/>
     </row>
-    <row r="18" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
         <v>64</v>
       </c>
@@ -9196,7 +9220,7 @@
       <c r="W18" s="24"/>
       <c r="X18" s="25"/>
     </row>
-    <row r="19" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A19" s="29" t="s">
         <v>1</v>
       </c>
@@ -9244,7 +9268,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:55" ht="65.400000000000006" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:55" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A20" s="27"/>
       <c r="B20" s="27"/>
       <c r="C20" s="13" t="s">
@@ -9354,7 +9378,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="21" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A21" s="16">
         <v>1</v>
       </c>
@@ -9444,7 +9468,7 @@
       </c>
       <c r="BC21" s="18"/>
     </row>
-    <row r="22" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>2</v>
       </c>
@@ -9533,7 +9557,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>3</v>
       </c>
@@ -9622,7 +9646,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>4</v>
       </c>
@@ -9711,7 +9735,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>5</v>
       </c>
@@ -9800,7 +9824,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>6</v>
       </c>
@@ -9889,7 +9913,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>7</v>
       </c>
@@ -9968,7 +9992,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="28" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>8</v>
       </c>
@@ -10047,7 +10071,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="29" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>9</v>
       </c>
@@ -10126,7 +10150,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="30" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>10</v>
       </c>
@@ -10205,7 +10229,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="31" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>11</v>
       </c>
@@ -10284,7 +10308,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="32" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>12</v>
       </c>
